--- a/demo/Recap_Test.xlsx
+++ b/demo/Recap_Test.xlsx
@@ -2,37 +2,38 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmarchio\Desktop\PROJECTS\prova pec massiva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0AD43B-8725-48E2-85E7-D6118C74D577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FA97F6-BB27-4DA7-9EC1-61ADDD863166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>ACME Industries Ltd.</t>
   </si>
@@ -131,6 +132,21 @@
   </si>
   <si>
     <t>office@silverline.com</t>
+  </si>
+  <si>
+    <t>COMPANY</t>
+  </si>
+  <si>
+    <t>CODE</t>
+  </si>
+  <si>
+    <t>VERSION</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
@@ -189,11 +205,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -498,167 +515,212 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <sheetPr codeName="Foglio1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2">
+        <f ca="1">TODAY()</f>
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E11" ca="1" si="0">TODAY()</f>
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E6" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E7" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="E8" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="E9" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="E10" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
+      <c r="E11" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>45972</v>
       </c>
     </row>
   </sheetData>
